--- a/public/upload/report/REKAP RAPOR YAYASAN PENDIDIKAN ALQALAM KENDARI (SDIT) TAHUN 2026.xlsx
+++ b/public/upload/report/REKAP RAPOR YAYASAN PENDIDIKAN ALQALAM KENDARI (SDIT) TAHUN 2026.xlsx
@@ -826,7 +826,9 @@
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -867,7 +869,9 @@
       <c r="B7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -908,7 +912,9 @@
       <c r="B8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -949,7 +955,9 @@
       <c r="B9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -990,7 +998,9 @@
       <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -1031,7 +1041,9 @@
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1072,7 +1084,9 @@
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1113,7 +1127,9 @@
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1154,7 +1170,9 @@
       <c r="B14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -1195,7 +1213,9 @@
       <c r="B15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -1236,7 +1256,9 @@
       <c r="B16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1277,7 +1299,9 @@
       <c r="B17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -1318,7 +1342,9 @@
       <c r="B18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -1359,7 +1385,9 @@
       <c r="B19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="3"/>
+      <c r="C19" s="3">
+        <v>0</v>
+      </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1400,7 +1428,9 @@
       <c r="B20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="3"/>
+      <c r="C20" s="3">
+        <v>0</v>
+      </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1441,7 +1471,9 @@
       <c r="B21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3">
+        <v>0</v>
+      </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -1482,7 +1514,9 @@
       <c r="B22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3">
+        <v>0</v>
+      </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -1523,7 +1557,9 @@
       <c r="B23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3">
+        <v>0</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -1564,7 +1600,9 @@
       <c r="B24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3">
+        <v>0</v>
+      </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -1605,7 +1643,9 @@
       <c r="B25" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="3"/>
+      <c r="C25" s="3">
+        <v>0</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1646,7 +1686,9 @@
       <c r="B26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="3"/>
+      <c r="C26" s="3">
+        <v>0</v>
+      </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -1687,7 +1729,9 @@
       <c r="B27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1728,7 +1772,9 @@
       <c r="B28" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3">
+        <v>0</v>
+      </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -1769,7 +1815,9 @@
       <c r="B29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="3"/>
+      <c r="C29" s="3">
+        <v>0</v>
+      </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -1810,7 +1858,9 @@
       <c r="B30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="3"/>
+      <c r="C30" s="3">
+        <v>0</v>
+      </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -1851,7 +1901,9 @@
       <c r="B31" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="3"/>
+      <c r="C31" s="3">
+        <v>0</v>
+      </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -1892,7 +1944,9 @@
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="3"/>
+      <c r="C32" s="3">
+        <v>0</v>
+      </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -1933,7 +1987,9 @@
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="3"/>
+      <c r="C33" s="3">
+        <v>0</v>
+      </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -1974,7 +2030,9 @@
       <c r="B34" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="3"/>
+      <c r="C34" s="3">
+        <v>0</v>
+      </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -2015,7 +2073,9 @@
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="3"/>
+      <c r="C35" s="3">
+        <v>0</v>
+      </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2056,7 +2116,9 @@
       <c r="B36" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="3"/>
+      <c r="C36" s="3">
+        <v>0</v>
+      </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2097,7 +2159,9 @@
       <c r="B37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="3"/>
+      <c r="C37" s="3">
+        <v>0</v>
+      </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -2138,7 +2202,9 @@
       <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C38" s="3"/>
+      <c r="C38" s="3">
+        <v>0</v>
+      </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2179,7 +2245,9 @@
       <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="3"/>
+      <c r="C39" s="3">
+        <v>0</v>
+      </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2220,7 +2288,9 @@
       <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="3"/>
+      <c r="C40" s="3">
+        <v>0</v>
+      </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -2261,7 +2331,9 @@
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C41" s="3"/>
+      <c r="C41" s="3">
+        <v>0</v>
+      </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -2302,7 +2374,9 @@
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C42" s="3"/>
+      <c r="C42" s="3">
+        <v>0</v>
+      </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -2343,7 +2417,9 @@
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="3"/>
+      <c r="C43" s="3">
+        <v>0</v>
+      </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -2384,7 +2460,9 @@
       <c r="B44" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="3"/>
+      <c r="C44" s="3">
+        <v>0</v>
+      </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -2425,7 +2503,9 @@
       <c r="B45" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C45" s="3"/>
+      <c r="C45" s="3">
+        <v>0</v>
+      </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -2466,7 +2546,9 @@
       <c r="B46" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C46" s="3"/>
+      <c r="C46" s="3">
+        <v>0</v>
+      </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -2507,7 +2589,9 @@
       <c r="B47" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C47" s="3"/>
+      <c r="C47" s="3">
+        <v>0</v>
+      </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -2548,7 +2632,9 @@
       <c r="B48" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="3"/>
+      <c r="C48" s="3">
+        <v>0</v>
+      </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -2589,7 +2675,9 @@
       <c r="B49" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="3"/>
+      <c r="C49" s="3">
+        <v>0</v>
+      </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -2630,7 +2718,9 @@
       <c r="B50" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="3"/>
+      <c r="C50" s="3">
+        <v>0</v>
+      </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -2671,7 +2761,9 @@
       <c r="B51" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C51" s="3"/>
+      <c r="C51" s="3">
+        <v>0</v>
+      </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -2712,7 +2804,9 @@
       <c r="B52" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C52" s="3"/>
+      <c r="C52" s="3">
+        <v>0</v>
+      </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -2753,7 +2847,9 @@
       <c r="B53" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C53" s="3"/>
+      <c r="C53" s="3">
+        <v>0</v>
+      </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -2794,7 +2890,9 @@
       <c r="B54" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C54" s="3"/>
+      <c r="C54" s="3">
+        <v>0</v>
+      </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -2835,7 +2933,9 @@
       <c r="B55" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="3"/>
+      <c r="C55" s="3">
+        <v>0</v>
+      </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -2876,7 +2976,9 @@
       <c r="B56" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C56" s="3"/>
+      <c r="C56" s="3">
+        <v>0</v>
+      </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -2917,7 +3019,9 @@
       <c r="B57" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C57" s="3"/>
+      <c r="C57" s="3">
+        <v>0</v>
+      </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -2958,7 +3062,9 @@
       <c r="B58" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C58" s="3"/>
+      <c r="C58" s="3">
+        <v>0</v>
+      </c>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -2999,7 +3105,9 @@
       <c r="B59" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C59" s="3"/>
+      <c r="C59" s="3">
+        <v>0</v>
+      </c>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
@@ -3040,7 +3148,9 @@
       <c r="B60" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="3"/>
+      <c r="C60" s="3">
+        <v>0</v>
+      </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -3081,7 +3191,9 @@
       <c r="B61" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C61" s="3"/>
+      <c r="C61" s="3">
+        <v>0</v>
+      </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
@@ -3122,7 +3234,9 @@
       <c r="B62" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C62" s="3"/>
+      <c r="C62" s="3">
+        <v>0</v>
+      </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
@@ -3163,7 +3277,9 @@
       <c r="B63" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="3"/>
+      <c r="C63" s="3">
+        <v>0</v>
+      </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
@@ -3204,7 +3320,9 @@
       <c r="B64" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C64" s="3"/>
+      <c r="C64" s="3">
+        <v>0</v>
+      </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -3245,7 +3363,9 @@
       <c r="B65" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C65" s="3"/>
+      <c r="C65" s="3">
+        <v>0</v>
+      </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
@@ -3286,7 +3406,9 @@
       <c r="B66" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C66" s="3"/>
+      <c r="C66" s="3">
+        <v>0</v>
+      </c>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
@@ -3327,7 +3449,9 @@
       <c r="B67" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C67" s="3"/>
+      <c r="C67" s="3">
+        <v>0</v>
+      </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -3368,7 +3492,9 @@
       <c r="B68" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C68" s="3"/>
+      <c r="C68" s="3">
+        <v>0</v>
+      </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
